--- a/survey_templates/030_dat_trainee_survey--survey_templates.xlsx
+++ b/survey_templates/030_dat_trainee_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>survey_title</t>
+          <t>Welcome to the DAT Trainee Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>What was your overall impression of the program?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>How likely are you to recommend this program to a friend or colleague?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>What aspects of the program did you find most valuable or useful?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>What aspects of the program did you find least valuable or confusing?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>How would you rate the quality of the instructors and facilitators?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>question_6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How would you rate the quality of the materials and resources provided?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select one of the following options -</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +690,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>How would you rate the overall organization and logistics of the program?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_question_8</t>
+          <t>dat_trainee_survey_question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>What suggestions do you have for improving the program?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,23 +726,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_question_9</t>
+          <t>dat_trainee_survey_question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>How likely are you to apply the knowledge and skills gained from this program in your work or personal life?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_question_10</t>
+          <t>dat_trainee_survey_question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>Have you attended any other programs or training events in the past year? If so, which ones?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_question_11</t>
+          <t>dat_trainee_survey_question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>Do you have any other comments or feedback about the program?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +800,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_question_12</t>
+          <t>dat_trainee_survey_page_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>Dat Trainee Survey Page 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,504 +818,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_question_13</t>
+          <t>dat_trainee_survey_page_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>Dat Trainee Survey Page 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_question_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_submitted_by</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_submit</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_title</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>survey_title</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_submitted_by</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_submit</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_category</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>survey_category</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_description</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>survey_description</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_id</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>survey_id</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_category</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>survey_category</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>dat_trainee_survey_survey_created_by</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1328,12 +849,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1356,102 +877,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_submit_choices</t>
+          <t>dat_trainee_survey_question_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'submit'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'submit'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_submit_choices</t>
+          <t>dat_trainee_survey_question_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'skip'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'skip'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_survey_submit_choices</t>
+          <t>dat_trainee_survey_question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'submit'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'submit'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_survey_submit_choices</t>
+          <t>dat_trainee_survey_question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'skip'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'skip'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_survey_category_choices</t>
+          <t>dat_trainee_survey_question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'survey_templates'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Survey Templates'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dat_trainee_survey_survey_category_choices</t>
+          <t>dat_trainee_survey_question_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'business_forms'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Business Forms'}</t>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_10_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Very Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_10_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>likely</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_10_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_10_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>somewhat_unlikely</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Somewhat Unlikely</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dat_trainee_survey_question_10_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>not_at_all_likely</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
